--- a/BeatnotePostHotCell/Jun10,2026/Fit_ResultJun10.xlsx
+++ b/BeatnotePostHotCell/Jun10,2026/Fit_ResultJun10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun10,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun10,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F04BCA-8014-49BB-A012-6D4060343485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51536959-F9C8-4B8F-B42F-FEAC19FE5C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Jun10,2026+1-58-17PM</t>
   </si>
   <si>
-    <t>Jun10,2026+2-06-24PM</t>
-  </si>
-  <si>
     <t>Jun10,2026+2-15-29PM</t>
   </si>
   <si>
@@ -122,9 +119,6 @@
     <t>Jun10,2026+1-32-10PM</t>
   </si>
   <si>
-    <t>Jun10,2026+1-41-03PM</t>
-  </si>
-  <si>
     <t>Jun10,2026+1-50-02PM</t>
   </si>
   <si>
@@ -137,9 +131,6 @@
     <t>Jun10,2026+10-17-51AM</t>
   </si>
   <si>
-    <t>Jun10,2026+10-33-44AM</t>
-  </si>
-  <si>
     <t>Jun10,2026+10-42-38AM</t>
   </si>
   <si>
@@ -155,18 +146,12 @@
     <t>Jun10,2026+11-21-47AM</t>
   </si>
   <si>
-    <t>Jun10,2026+11-29-52AM</t>
-  </si>
-  <si>
     <t>Jun10,2026+11-45-04AM</t>
   </si>
   <si>
     <t>Jun10,2026+11-53-19AM</t>
   </si>
   <si>
-    <t>Jun10,2026+12-15-54PM</t>
-  </si>
-  <si>
     <t>Jun10,2026+12-25-01PM</t>
   </si>
   <si>
@@ -174,12 +159,6 @@
   </si>
   <si>
     <t>Jun10,2026+12-41-09PM</t>
-  </si>
-  <si>
-    <t>Jun10,2026+12-49-04PM</t>
-  </si>
-  <si>
-    <t>Jun10,2026+12-57-09PM</t>
   </si>
   <si>
     <t>Mean</t>
@@ -195,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,9 +546,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -603,9 +582,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="42.75">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
         <v>7.0733851626533504</v>
@@ -628,9 +607,9 @@
       <c r="H2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
         <v>7.0645821415754702</v>
@@ -653,9 +632,9 @@
       <c r="H3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>7.0594232243202404</v>
@@ -678,9 +657,9 @@
       <c r="H4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>7.0595369414161802</v>
@@ -703,9 +682,9 @@
       <c r="H5" s="1"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>7.1355028757261403</v>
@@ -728,9 +707,9 @@
       <c r="H6" s="1"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1">
         <v>7.1742988315936698</v>
@@ -753,9 +732,9 @@
       <c r="H7" s="1"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>7.2143004246012596</v>
@@ -778,9 +757,9 @@
       <c r="H8" s="1"/>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1">
         <v>7.1896716464449897</v>
@@ -803,9 +782,9 @@
       <c r="H9" s="1"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>7.0740088746791701</v>
@@ -828,9 +807,9 @@
       <c r="H10" s="1"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>7.1243444840245997</v>
@@ -853,9 +832,9 @@
       <c r="H11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1">
         <v>7.0585349758452001</v>
@@ -878,9 +857,9 @@
       <c r="H12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1">
         <v>7.0753396553470003</v>
@@ -903,9 +882,9 @@
       <c r="H13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1">
         <v>7.0929763944296802</v>
@@ -928,9 +907,9 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1">
         <v>7.1058506533772503</v>
@@ -953,9 +932,9 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1">
         <v>7.1002899790140797</v>
@@ -978,9 +957,9 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
         <v>7.0521776395148397</v>
@@ -1002,9 +981,9 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1">
         <v>7.1167399746803</v>
@@ -1026,7 +1005,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -1050,9 +1029,9 @@
       </c>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1">
         <v>7.1580456374110897</v>
@@ -1074,9 +1053,9 @@
       </c>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1">
         <v>7.2190634878376496</v>
@@ -1098,9 +1077,9 @@
       </c>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1">
         <v>7.2062880356903998</v>
@@ -1121,9 +1100,9 @@
         <v>2.2873004957460999E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1">
         <v>7.1744031277414697</v>
@@ -1144,9 +1123,9 @@
         <v>2.2873004957064801E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
         <v>7.1782561712895996</v>
@@ -1167,9 +1146,9 @@
         <v>2.28730049570141E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
         <v>7.1789296294298</v>
@@ -1190,9 +1169,9 @@
         <v>2.2873004958968101E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
         <v>7.1380410516405304</v>
@@ -1213,9 +1192,9 @@
         <v>2.2873004957051002E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="42.75">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1">
         <v>7.1009576964689503</v>
@@ -1236,9 +1215,9 @@
         <v>2.4942052655924198E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="42.75">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1">
         <v>7.1095475512566804</v>
@@ -1259,9 +1238,9 @@
         <v>2.3425024242361898E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="42.75">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1">
         <v>7.1520505928297498</v>
@@ -1282,9 +1261,9 @@
         <v>2.5594812956546398E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="42.75">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="1">
         <v>7.1324554911158904</v>
@@ -1305,9 +1284,9 @@
         <v>2.28730049570362E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1">
         <v>7.1772995060305798</v>
@@ -1328,9 +1307,9 @@
         <v>2.2873004957052602E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <v>7.13962874760949</v>
@@ -1351,9 +1330,9 @@
         <v>2.2873004993176002E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="42.75">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" s="1">
         <v>7.1606128880127899</v>
@@ -1382,9 +1361,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1419,12 +1398,12 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
-        <v>0.117218052017694</v>
+        <v>9.1307178056809907E-2</v>
       </c>
       <c r="C2" s="1">
         <v>1.47574630490105</v>
@@ -1436,21 +1415,21 @@
         <v>2.68272305608428E-5</v>
       </c>
       <c r="F2" s="1">
-        <v>2.2273611015762098</v>
+        <v>2.1661800600525698</v>
       </c>
       <c r="G2" s="1">
-        <v>60.793101660976298</v>
+        <v>60.803413031243402</v>
       </c>
       <c r="H2" s="1">
-        <v>6.3579365799506604E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1767315460803899E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
-        <v>0.116738218899043</v>
+        <v>9.0851652530901106E-2</v>
       </c>
       <c r="C3" s="1">
         <v>1.4748889513194401</v>
@@ -1462,21 +1441,21 @@
         <v>-6.8366635643412406E-5</v>
       </c>
       <c r="F3" s="1">
-        <v>2.6865674598556799</v>
+        <v>2.6253854612915299</v>
       </c>
       <c r="G3" s="1">
-        <v>62.107612451032601</v>
+        <v>61.795182445185198</v>
       </c>
       <c r="H3" s="1">
-        <v>1.0722400524266101E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5220717136789596E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
-        <v>0.116641895814922</v>
+        <v>9.0871105956180601E-2</v>
       </c>
       <c r="C4" s="1">
         <v>1.4747765701935101</v>
@@ -1488,950 +1467,838 @@
         <v>4.7838035742508899E-5</v>
       </c>
       <c r="F4" s="1">
-        <v>1.9745546640859299</v>
+        <v>1.9133702477976</v>
       </c>
       <c r="G4" s="1">
-        <v>60.772397273331798</v>
+        <v>60.788857451582203</v>
       </c>
       <c r="H4" s="1">
-        <v>5.8153774867740905E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.4856972733999697E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="1">
+        <v>9.1887059128850701E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.4742694512377501</v>
+      </c>
+      <c r="D5" s="1">
+        <v>-6.6744942891326599E-4</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.7075223340194702E-5</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1.91737514852933</v>
+      </c>
+      <c r="G5" s="1">
+        <v>62.738653372552299</v>
+      </c>
+      <c r="H5" s="1">
+        <v>9.7420466209548597E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="1">
+        <v>9.0625181514815994E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.4751113530112301</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-7.2066843821110504E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4.0000234563253799E-5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1.9255281911790501</v>
+      </c>
+      <c r="G6" s="1">
+        <v>60.745637722279298</v>
+      </c>
+      <c r="H6" s="1">
+        <v>5.7884250262370902E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
+      <c r="A7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="1">
-        <v>0.11248563271776001</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1.4744227547789099</v>
-      </c>
-      <c r="D5" s="1">
-        <v>-6.4164405375229702E-4</v>
-      </c>
-      <c r="E5" s="2">
-        <v>2.50590778074886E-5</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1.9760119101032101</v>
-      </c>
-      <c r="G5" s="1">
-        <v>60.723982285018501</v>
-      </c>
-      <c r="H5" s="1">
-        <v>6.4240363832248498E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="B7" s="1">
+        <v>9.19073278180111E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.4752031768018401</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-4.5145011633356501E-4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>-1.5281675459127898E-5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2.1729819221617799</v>
+      </c>
+      <c r="G7" s="1">
+        <v>62.714248484122898</v>
+      </c>
+      <c r="H7" s="1">
+        <v>9.3788783293620101E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
+      <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="1">
-        <v>0.117986722306339</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1.4742694512377501</v>
-      </c>
-      <c r="D6" s="1">
-        <v>-6.6744942891326599E-4</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.7075223340194702E-5</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1.9785331683152201</v>
-      </c>
-      <c r="G6" s="1">
-        <v>62.706896092859303</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1.02641560302921E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="B8" s="1">
+        <v>9.16991502213306E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.47586956038813</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-9.45874426810827E-4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>7.2081149556097205E-5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2.1735156576172101</v>
+      </c>
+      <c r="G8" s="1">
+        <v>60.803019190251902</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5.7860596317692E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.116363944216263</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1.4751113530112301</v>
-      </c>
-      <c r="D7" s="1">
-        <v>-7.2066843821110504E-4</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4.0000234563253799E-5</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1.9866996217808199</v>
-      </c>
-      <c r="G7" s="1">
-        <v>60.745668865732299</v>
-      </c>
-      <c r="H7" s="1">
-        <v>5.8805886347450698E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1">
+        <v>9.2126787185543096E-2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.47480542370045</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1.20281484929041E-4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>-9.9941212348104199E-5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2.42429833428687</v>
+      </c>
+      <c r="G9" s="1">
+        <v>60.761453496533498</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6.0850027367507099E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
+      <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="1">
-        <v>0.117960737624138</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1.4752031768018401</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-4.5145011633356501E-4</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-1.5281675459127898E-5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2.2341535240539399</v>
-      </c>
-      <c r="G8" s="1">
-        <v>62.2860390082948</v>
-      </c>
-      <c r="H8" s="1">
-        <v>8.9228691644675795E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="1">
+        <v>9.2487262159234904E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.4750888661585799</v>
+      </c>
+      <c r="D10" s="1">
+        <v>-1.8199348947547001E-4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>-7.7956608582161306E-5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1.6650521169733801</v>
+      </c>
+      <c r="G10" s="1">
+        <v>62.785489835424201</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1.09440750596835E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
+      <c r="A11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="1">
-        <v>0.11777189549636199</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1.47586956038813</v>
-      </c>
-      <c r="D9" s="1">
-        <v>-9.45874426810827E-4</v>
-      </c>
-      <c r="E9" s="2">
-        <v>7.2081149556097205E-5</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2.2346795705809499</v>
-      </c>
-      <c r="G9" s="1">
-        <v>60.741931554557297</v>
-      </c>
-      <c r="H9" s="1">
-        <v>7.6557598549494802E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="B11" s="1">
+        <v>9.2057197677155297E-2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.4745341606523701</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-5.1243429519438302E-4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>-1.86498726544234E-5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2.1679986527984498</v>
+      </c>
+      <c r="G11" s="1">
+        <v>62.6057956807539</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1.1536829781767699E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
+      <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="1">
-        <v>0.118362346500101</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1.47480542370045</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1.20281484929041E-4</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-9.9941212348104199E-5</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2.4854761022802099</v>
-      </c>
-      <c r="G10" s="1">
-        <v>61.214324322250697</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7.9731109954564103E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="B12" s="1">
+        <v>9.0785728319137698E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.47565197500262</v>
+      </c>
+      <c r="D12" s="1">
+        <v>-2.29264814925449E-4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>-6.3872136284176694E-5</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.6706857352761</v>
+      </c>
+      <c r="G12" s="1">
+        <v>60.829077350159402</v>
+      </c>
+      <c r="H12" s="1">
+        <v>6.4164219877300803E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
+      <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1">
-        <v>0.115218928402134</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1.47549843692822</v>
-      </c>
-      <c r="D11" s="1">
-        <v>-1.8424223746639501E-4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>-6.6834669423921695E-5</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2.5438028796137901</v>
-      </c>
-      <c r="G11" s="1">
-        <v>60.773975121545099</v>
-      </c>
-      <c r="H11" s="1">
-        <v>6.1123013451975399E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="B13" s="1">
+        <v>9.1583374078481494E-2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1.4758470480227399</v>
+      </c>
+      <c r="D13" s="1">
+        <v>-4.6152165860934702E-4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>-2.5606631226033701E-5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1.62208735429421</v>
+      </c>
+      <c r="G13" s="1">
+        <v>61.043991224385501</v>
+      </c>
+      <c r="H13" s="1">
+        <v>6.5462325859428803E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
+      <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="1">
-        <v>0.11875028071223</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1.4750888661585799</v>
-      </c>
-      <c r="D12" s="1">
-        <v>-1.8199348947547001E-4</v>
-      </c>
-      <c r="E12" s="2">
-        <v>-7.7956608582161306E-5</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1.72618110943022</v>
-      </c>
-      <c r="G12" s="1">
-        <v>62.630018779787598</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1.1563092025745801E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0.118209453954305</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1.4745341606523701</v>
-      </c>
-      <c r="D13" s="1">
-        <v>-5.1243429519438302E-4</v>
-      </c>
-      <c r="E13" s="2">
-        <v>-1.86498726544234E-5</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2.2291402175722799</v>
-      </c>
-      <c r="G13" s="1">
-        <v>62.798924076552701</v>
-      </c>
-      <c r="H13" s="1">
-        <v>1.1318685217634899E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="B14" s="1">
-        <v>0.112666943057704</v>
+        <v>9.1977352407887902E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>1.4749162287895099</v>
-      </c>
-      <c r="D14" s="1">
-        <v>-4.9253688677690702E-4</v>
+        <v>1.4750807638321399</v>
+      </c>
+      <c r="D14" s="2">
+        <v>7.1832015214206196E-6</v>
       </c>
       <c r="E14" s="2">
-        <v>-1.3680429389250701E-5</v>
+        <v>-9.1688093633735795E-5</v>
       </c>
       <c r="F14" s="1">
-        <v>2.4429138956280299</v>
+        <v>1.91965998175335</v>
       </c>
       <c r="G14" s="1">
-        <v>60.8162388841519</v>
+        <v>61.011210091920802</v>
       </c>
       <c r="H14" s="1">
-        <v>5.8271556032690101E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.4640986847412803E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1">
-        <v>0.116577694816434</v>
+        <v>9.0809253307868806E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>1.47565197500262</v>
+        <v>1.47543699306106</v>
       </c>
       <c r="D15" s="1">
-        <v>-2.29264814925449E-4</v>
+        <v>-8.1069790130807796E-4</v>
       </c>
       <c r="E15" s="2">
-        <v>-6.3872136284176694E-5</v>
+        <v>9.2769668633032993E-5</v>
       </c>
       <c r="F15" s="1">
-        <v>1.7318567783995999</v>
+        <v>1.9120878438111399</v>
       </c>
       <c r="G15" s="1">
-        <v>60.850869367134599</v>
+        <v>60.897902275380801</v>
       </c>
       <c r="H15" s="1">
-        <v>6.7505671579061997E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.9548062583492099E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1">
-        <v>0.117670638852321</v>
+        <v>9.2274633741869796E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>1.4758470480227399</v>
+        <v>1.4748856461734301</v>
       </c>
       <c r="D16" s="1">
-        <v>-4.6152165860934702E-4</v>
+        <v>-2.5101310028236397E-4</v>
       </c>
       <c r="E16" s="2">
-        <v>-2.5606631226033701E-5</v>
+        <v>5.0681333992978002E-6</v>
       </c>
       <c r="F16" s="1">
-        <v>1.6832675131666801</v>
+        <v>1.9206344558619499</v>
       </c>
       <c r="G16" s="1">
-        <v>60.845894662885499</v>
+        <v>62.932428214614603</v>
       </c>
       <c r="H16" s="1">
-        <v>1.1305102244806701E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.01983352526956E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
-        <v>0.118098845799444</v>
+        <v>9.1163861413001701E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>1.4750807638321399</v>
+        <v>1.47478957635837</v>
       </c>
       <c r="D17" s="2">
-        <v>7.1832015214206196E-6</v>
+        <v>-3.4792463370420798E-5</v>
       </c>
       <c r="E17" s="2">
-        <v>-9.1688093633735795E-5</v>
+        <v>-4.8890651156557901E-5</v>
       </c>
       <c r="F17" s="1">
-        <v>1.98082629519836</v>
+        <v>2.12229884251339</v>
       </c>
       <c r="G17" s="1">
-        <v>61.065029917009198</v>
+        <v>60.924935355579898</v>
       </c>
       <c r="H17" s="1">
-        <v>6.4275037717725198E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.2083883990402997E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1">
-        <v>0.11579122267429801</v>
+        <v>9.1080103179609503E-2</v>
       </c>
       <c r="C18" s="1">
-        <v>1.4756226853465</v>
+        <v>1.4752025976155501</v>
       </c>
       <c r="D18" s="1">
-        <v>-5.7624635844757597E-4</v>
+        <v>-4.6117571072579303E-4</v>
       </c>
       <c r="E18" s="2">
-        <v>1.3472086682061799E-5</v>
+        <v>1.7990017937014601E-5</v>
       </c>
       <c r="F18" s="1">
-        <v>1.98822294908533</v>
+        <v>1.9151953700740101</v>
       </c>
       <c r="G18" s="1">
-        <v>60.851367968198701</v>
+        <v>60.940228208298201</v>
       </c>
       <c r="H18" s="1">
-        <v>5.80781513588563E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.2661736263980104E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1">
-        <v>0.115462934360178</v>
+        <v>9.1489922352594399E-2</v>
       </c>
       <c r="C19" s="1">
-        <v>1.4746822974385601</v>
-      </c>
-      <c r="D19" s="1">
-        <v>-3.7604084380489701E-4</v>
+        <v>1.4744183266064099</v>
+      </c>
+      <c r="D19" s="2">
+        <v>-5.4702927951104899E-5</v>
       </c>
       <c r="E19" s="2">
-        <v>5.4015496176959898E-6</v>
+        <v>-4.2319216853115399E-5</v>
       </c>
       <c r="F19" s="1">
-        <v>1.72746695410948</v>
+        <v>1.91404139915278</v>
       </c>
       <c r="G19" s="1">
-        <v>60.903007523977898</v>
+        <v>60.958908286460698</v>
       </c>
       <c r="H19" s="1">
-        <v>6.1434001622349597E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.9708267291539103E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1">
-        <v>0.11655919684067299</v>
+        <v>9.24749435955321E-2</v>
       </c>
       <c r="C20" s="1">
-        <v>1.47543699306106</v>
+        <v>1.4752524278182999</v>
       </c>
       <c r="D20" s="1">
-        <v>-8.1069790130807796E-4</v>
+        <v>-2.14598368332037E-4</v>
       </c>
       <c r="E20" s="2">
-        <v>9.2769668633032993E-5</v>
+        <v>1.2653139303334501E-6</v>
       </c>
       <c r="F20" s="1">
-        <v>1.9732869687458701</v>
+        <v>1.92002685680198</v>
       </c>
       <c r="G20" s="1">
-        <v>60.908396841306001</v>
+        <v>62.965170602404903</v>
       </c>
       <c r="H20" s="1">
-        <v>5.9559715678698705E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0975980595398201E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1">
-        <v>0.118487075826876</v>
+        <v>9.2335401313700993E-2</v>
       </c>
       <c r="C21" s="1">
-        <v>1.4748856461734301</v>
+        <v>1.4754733037732399</v>
       </c>
       <c r="D21" s="1">
-        <v>-2.5101310028236397E-4</v>
+        <v>-3.0822468150292501E-4</v>
       </c>
       <c r="E21" s="2">
-        <v>5.0681333992978002E-6</v>
+        <v>-2.9572103696778001E-6</v>
       </c>
       <c r="F21" s="1">
-        <v>1.9817967971097601</v>
+        <v>1.9200626567533601</v>
       </c>
       <c r="G21" s="1">
-        <v>62.883181992292002</v>
+        <v>62.930530319342502</v>
       </c>
       <c r="H21" s="1">
-        <v>1.08770098509087E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0638119094143301E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1">
-        <v>0.117049111989703</v>
+        <v>9.1016046887435004E-2</v>
       </c>
       <c r="C22" s="1">
-        <v>1.47478957635837</v>
-      </c>
-      <c r="D22" s="2">
-        <v>-3.4792463370420798E-5</v>
+        <v>1.47572268646491</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-6.0971004276074597E-4</v>
       </c>
       <c r="E22" s="2">
-        <v>-4.8890651156557901E-5</v>
+        <v>3.8077624560930502E-5</v>
       </c>
       <c r="F22" s="1">
-        <v>2.18348957476698</v>
+        <v>1.8709816837366799</v>
       </c>
       <c r="G22" s="1">
-        <v>60.995280838427298</v>
+        <v>61.011290621370598</v>
       </c>
       <c r="H22" s="1">
-        <v>5.7867707821156005E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.4499096552396397E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1">
-        <v>0.11382696379874201</v>
+        <v>9.1793854609833803E-2</v>
       </c>
       <c r="C23" s="1">
-        <v>1.4750292445755799</v>
+        <v>1.4748083408317101</v>
       </c>
       <c r="D23" s="1">
-        <v>-3.6022392139603099E-4</v>
+        <v>-2.10741796270059E-4</v>
       </c>
       <c r="E23" s="2">
-        <v>1.00407888036818E-5</v>
+        <v>-1.24398879094679E-5</v>
       </c>
       <c r="F23" s="1">
-        <v>1.9893309280810501</v>
+        <v>1.6725394492021901</v>
       </c>
       <c r="G23" s="1">
-        <v>60.9472221004728</v>
+        <v>61.2854127091978</v>
       </c>
       <c r="H23" s="1">
-        <v>5.7857693437686497E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9465452136565102E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
-        <v>0.116964493443121</v>
+        <v>9.0459757856193396E-2</v>
       </c>
       <c r="C24" s="1">
-        <v>1.4752025976155501</v>
+        <v>1.4749732464056799</v>
       </c>
       <c r="D24" s="1">
-        <v>-4.6117571072579303E-4</v>
+        <v>-2.8720091398010301E-4</v>
       </c>
       <c r="E24" s="2">
-        <v>1.7990017937014601E-5</v>
+        <v>-1.3168335264833401E-8</v>
       </c>
       <c r="F24" s="1">
-        <v>1.9763802822916701</v>
+        <v>1.6732477956977001</v>
       </c>
       <c r="G24" s="1">
-        <v>60.936817694798499</v>
+        <v>61.007766373105198</v>
       </c>
       <c r="H24" s="1">
-        <v>8.3485843070444299E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0871518241884496E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
-        <v>0.1174932059815</v>
+        <v>9.0535769763873494E-2</v>
       </c>
       <c r="C25" s="1">
-        <v>1.4744183266064099</v>
-      </c>
-      <c r="D25" s="2">
-        <v>-5.4702927951104899E-5</v>
+        <v>1.4745782713770501</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-6.5640648284887395E-4</v>
       </c>
       <c r="E25" s="2">
-        <v>-4.2319216853115399E-5</v>
+        <v>7.5911006603723494E-5</v>
       </c>
       <c r="F25" s="1">
-        <v>1.9752157757232101</v>
+        <v>1.66752686146092</v>
       </c>
       <c r="G25" s="1">
-        <v>60.988758779755599</v>
+        <v>61.130117670667303</v>
       </c>
       <c r="H25" s="1">
-        <v>6.9089868678139598E-4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.1415803825133695E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
-        <v>0.115439704596003</v>
+        <v>9.2308774170074298E-2</v>
       </c>
       <c r="C26" s="1">
-        <v>1.4749155937424601</v>
+        <v>1.4735105169051499</v>
       </c>
       <c r="D26" s="1">
-        <v>-1.9776280253540199E-4</v>
+        <v>-2.825476197615E-4</v>
       </c>
       <c r="E26" s="2">
-        <v>-8.4595454527815304E-6</v>
+        <v>3.02315670134319E-5</v>
       </c>
       <c r="F26" s="1">
-        <v>1.9767466651880301</v>
+        <v>1.6704846932283901</v>
       </c>
       <c r="G26" s="1">
-        <v>60.969691672600497</v>
+        <v>62.017779771005301</v>
       </c>
       <c r="H26" s="1">
-        <v>6.5954852297093905E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5220681883575804E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="42.75">
       <c r="A27" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1">
-        <v>0.118724780988732</v>
+        <v>9.169315182519E-2</v>
       </c>
       <c r="C27" s="1">
-        <v>1.4752524278182999</v>
+        <v>1.4756596303716001</v>
       </c>
       <c r="D27" s="1">
-        <v>-2.14598368332037E-4</v>
+        <v>-6.2614506864232895E-4</v>
       </c>
       <c r="E27" s="2">
-        <v>1.2653139303334501E-6</v>
+        <v>3.4492035987373903E-5</v>
       </c>
       <c r="F27" s="1">
-        <v>1.9811974088833499</v>
+        <v>2.16391351747097</v>
       </c>
       <c r="G27" s="1">
-        <v>62.942094934564601</v>
+        <v>61.166029480164298</v>
       </c>
       <c r="H27" s="1">
-        <v>1.0700538889500801E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.84929196546356E-4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="42.75">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1">
-        <v>0.11857414162119</v>
+        <v>9.0973320989362394E-2</v>
       </c>
       <c r="C28" s="1">
-        <v>1.4754733037732399</v>
+        <v>1.47529028195024</v>
       </c>
       <c r="D28" s="1">
-        <v>-3.0822468150292501E-4</v>
+        <v>-4.75851676415939E-4</v>
       </c>
       <c r="E28" s="2">
-        <v>-2.9572103696778001E-6</v>
+        <v>2.64696338197679E-5</v>
       </c>
       <c r="F28" s="1">
-        <v>1.9812101828334101</v>
+        <v>1.87249818243616</v>
       </c>
       <c r="G28" s="1">
-        <v>62.973267728712003</v>
+        <v>61.1304401655023</v>
       </c>
       <c r="H28" s="1">
-        <v>1.1569324277096501E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9963378125387601E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="42.75">
       <c r="A29" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1">
-        <v>0.116857985488521</v>
+        <v>9.2289486690982594E-2</v>
       </c>
       <c r="C29" s="1">
-        <v>1.47572268646491</v>
+        <v>1.4753145534094401</v>
       </c>
       <c r="D29" s="1">
-        <v>-6.0971004276074597E-4</v>
+        <v>-2.62478984227781E-4</v>
       </c>
       <c r="E29" s="2">
-        <v>3.8077624560930502E-5</v>
+        <v>-2.6350627289203901E-5</v>
       </c>
       <c r="F29" s="1">
-        <v>1.9321625296282601</v>
+        <v>1.91290888576643</v>
       </c>
       <c r="G29" s="1">
-        <v>60.994241175690298</v>
+        <v>61.089620319872097</v>
       </c>
       <c r="H29" s="1">
-        <v>6.3052164343179297E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.7858349051449396E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="42.75">
       <c r="A30" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B30" s="1">
-        <v>0.117839930521939</v>
+        <v>9.2332804146897596E-2</v>
       </c>
       <c r="C30" s="1">
-        <v>1.4748083408317101</v>
+        <v>1.4753934464638401</v>
       </c>
       <c r="D30" s="1">
-        <v>-2.10741796270059E-4</v>
+        <v>-4.3607733226335799E-4</v>
       </c>
       <c r="E30" s="2">
-        <v>-1.24398879094679E-5</v>
+        <v>-7.6495971731603304E-7</v>
       </c>
       <c r="F30" s="1">
-        <v>1.73371157373878</v>
+        <v>1.9127512624224701</v>
       </c>
       <c r="G30" s="1">
-        <v>60.994872990334201</v>
+        <v>61.071936499928597</v>
       </c>
       <c r="H30" s="1">
-        <v>7.0466883170324196E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.3854790604133001E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="42.75">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1">
-        <v>0.116123290748398</v>
+        <v>9.1338576946075195E-2</v>
       </c>
       <c r="C31" s="1">
-        <v>1.4749732464056799</v>
+        <v>1.47500236723988</v>
       </c>
       <c r="D31" s="1">
-        <v>-2.8720091398010301E-4</v>
+        <v>-4.2923020227059498E-4</v>
       </c>
       <c r="E31" s="2">
-        <v>-1.3168335264833401E-8</v>
+        <v>6.5288898109104896E-6</v>
       </c>
       <c r="F31" s="1">
-        <v>1.7344296481600501</v>
+        <v>1.90695262069342</v>
       </c>
       <c r="G31" s="1">
-        <v>61.007065052459801</v>
+        <v>61.149817082080503</v>
       </c>
       <c r="H31" s="1">
-        <v>5.82506164344971E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5.8046128299823097E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="42.75">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
-        <v>0.116339626646247</v>
+        <v>9.2043650053371201E-2</v>
       </c>
       <c r="C32" s="1">
-        <v>1.4745782713770501</v>
+        <v>1.4752342120084601</v>
       </c>
       <c r="D32" s="1">
-        <v>-6.5640648284887395E-4</v>
+        <v>-4.4549507123329402E-4</v>
       </c>
       <c r="E32" s="2">
-        <v>7.5911006603723494E-5</v>
+        <v>2.25478137392743E-6</v>
       </c>
       <c r="F32" s="1">
-        <v>1.7287254388723601</v>
+        <v>2.12464762728542</v>
       </c>
       <c r="G32" s="1">
-        <v>61.998884815073801</v>
+        <v>63.022530208506097</v>
       </c>
       <c r="H32" s="1">
-        <v>7.52206220616932E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.8398053658976399E-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="42.75">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B33" s="1">
-        <v>0.118521454357363</v>
+        <v>9.2039900597932794E-2</v>
       </c>
       <c r="C33" s="1">
-        <v>1.4735105169051499</v>
-      </c>
-      <c r="D33" s="1">
-        <v>-2.825476197615E-4</v>
+        <v>1.47523686867126</v>
+      </c>
+      <c r="D33" s="2">
+        <v>-5.4803270487520203E-5</v>
       </c>
       <c r="E33" s="2">
-        <v>3.02315670134319E-5</v>
+        <v>-6.8346955520591903E-5</v>
       </c>
       <c r="F33" s="1">
-        <v>1.7316511415048601</v>
+        <v>2.1287330441410099</v>
       </c>
       <c r="G33" s="1">
-        <v>62.017771865447997</v>
+        <v>62.921083226706401</v>
       </c>
       <c r="H33" s="1">
-        <v>7.5220540434781102E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="1">
-        <v>0.117743388207075</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1.4756596303716001</v>
-      </c>
-      <c r="D34" s="1">
-        <v>-6.2614506864232895E-4</v>
-      </c>
-      <c r="E34" s="2">
-        <v>3.4492035987373903E-5</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2.2250925213633499</v>
-      </c>
-      <c r="G34" s="1">
-        <v>61.336596103246102</v>
-      </c>
-      <c r="H34" s="1">
-        <v>5.80029147208132E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" s="1">
-        <v>0.116823099810358</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1.47529028195024</v>
-      </c>
-      <c r="D35" s="1">
-        <v>-4.75851676415939E-4</v>
-      </c>
-      <c r="E35" s="2">
-        <v>2.64696338197679E-5</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1.9336838124848601</v>
-      </c>
-      <c r="G35" s="1">
-        <v>61.385432393339002</v>
-      </c>
-      <c r="H35" s="1">
-        <v>6.85413495181085E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" s="1">
-        <v>0.118509294607666</v>
-      </c>
-      <c r="C36" s="1">
-        <v>1.4753145534094401</v>
-      </c>
-      <c r="D36" s="1">
-        <v>-2.62478984227781E-4</v>
-      </c>
-      <c r="E36" s="2">
-        <v>-2.6350627289203901E-5</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1.9741030881767001</v>
-      </c>
-      <c r="G36" s="1">
-        <v>61.055520661869501</v>
-      </c>
-      <c r="H36" s="1">
-        <v>6.5889055791112396E-4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="1">
-        <v>0.118631007440724</v>
-      </c>
-      <c r="C37" s="1">
-        <v>1.4753934464638401</v>
-      </c>
-      <c r="D37" s="1">
-        <v>-4.3607733226335799E-4</v>
-      </c>
-      <c r="E37" s="2">
-        <v>-7.6495971731603304E-7</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1.97393134199472</v>
-      </c>
-      <c r="G37" s="1">
-        <v>62.203948450266203</v>
-      </c>
-      <c r="H37" s="1">
-        <v>5.8226754429283295E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="1">
-        <v>0.117484320873481</v>
-      </c>
-      <c r="C38" s="1">
-        <v>1.47500236723988</v>
-      </c>
-      <c r="D38" s="1">
-        <v>-4.2923020227059498E-4</v>
-      </c>
-      <c r="E38" s="2">
-        <v>6.5288898109104896E-6</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1.9681376862822799</v>
-      </c>
-      <c r="G38" s="1">
-        <v>63.000564860631897</v>
-      </c>
-      <c r="H38" s="1">
-        <v>8.93078723405695E-4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="1">
-        <v>0.118251546607688</v>
-      </c>
-      <c r="C39" s="1">
-        <v>1.4752342120084601</v>
-      </c>
-      <c r="D39" s="1">
-        <v>-4.4549507123329402E-4</v>
-      </c>
-      <c r="E39" s="2">
-        <v>2.25478137392743E-6</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2.18581088304038</v>
-      </c>
-      <c r="G39" s="1">
-        <v>63.040957378456397</v>
-      </c>
-      <c r="H39" s="1">
-        <v>1.0279075782588199E-3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="1">
-        <v>0.118181098472526</v>
-      </c>
-      <c r="C40" s="1">
-        <v>1.47523686867126</v>
-      </c>
-      <c r="D40" s="2">
-        <v>-5.4803270487520203E-5</v>
-      </c>
-      <c r="E40" s="2">
-        <v>-6.8346955520591903E-5</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2.1898951538405802</v>
-      </c>
-      <c r="G40" s="1">
-        <v>62.989237369559802</v>
-      </c>
-      <c r="H40" s="1">
-        <v>1.15510971828036E-3</v>
-      </c>
+        <v>1.1554515923016199E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2440,13 +2307,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N33"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="7" max="7" width="16.7265625" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2457,15 +2324,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="42.75">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
         <v>7.0733851626533504</v>
       </c>
       <c r="C2" s="1">
-        <v>0.117218052017694</v>
+        <v>9.1307178056809907E-2</v>
       </c>
       <c r="H2">
         <v>894</v>
@@ -2473,19 +2340,20 @@
       <c r="I2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
         <v>7.0645821415754702</v>
       </c>
       <c r="C3" s="1">
-        <v>0.116738218899043</v>
+        <v>9.0851652530901106E-2</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <f>AVERAGE(B2:B33)</f>
@@ -2493,21 +2361,22 @@
       </c>
       <c r="I3">
         <f>AVERAGE(C2:C33)</f>
-        <v>0.11760964929635552</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1581861577991877E-2</v>
+      </c>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>7.0594232243202404</v>
       </c>
       <c r="C4" s="1">
-        <v>0.116641895814922</v>
+        <v>9.0871105956180601E-2</v>
       </c>
       <c r="G4" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H4">
         <f>_xlfn.STDEV.S(B2:B33)</f>
@@ -2515,21 +2384,22 @@
       </c>
       <c r="I4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>8.1387659506700614E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.3318185062280702E-4</v>
+      </c>
+      <c r="N4" s="1"/>
+    </row>
+    <row r="5" spans="1:14" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>7.0595369414161802</v>
       </c>
       <c r="C5" s="1">
-        <v>0.117986722306339</v>
+        <v>9.1887059128850701E-2</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H5">
         <f>H4/H3/SQRT(COUNT(B2:B33))</f>
@@ -2537,153 +2407,167 @@
       </c>
       <c r="I5">
         <f>I4/I3/SQRT(COUNT(C2:C33))</f>
-        <v>1.2233215192461494E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.2222048465305169E-3</v>
+      </c>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B6" s="1">
         <v>7.1355028757261403</v>
       </c>
       <c r="C6" s="1">
-        <v>0.116363944216263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0625181514815994E-2</v>
+      </c>
+      <c r="N6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1">
         <v>7.1742988315936698</v>
       </c>
       <c r="C7" s="1">
-        <v>0.117960737624138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.19073278180111E-2</v>
+      </c>
+      <c r="N7" s="1"/>
+    </row>
+    <row r="8" spans="1:14" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1">
         <v>7.2143004246012596</v>
       </c>
       <c r="C8" s="1">
-        <v>0.11777189549636199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.16991502213306E-2</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1">
         <v>7.1896716464449897</v>
       </c>
       <c r="C9" s="1">
-        <v>0.118362346500101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2126787185543096E-2</v>
+      </c>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>7.0740088746791701</v>
       </c>
       <c r="C10" s="1">
-        <v>0.11875028071223</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2487262159234904E-2</v>
+      </c>
+      <c r="N10" s="1"/>
+    </row>
+    <row r="11" spans="1:14" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="1">
         <v>7.1243444840245997</v>
       </c>
       <c r="C11" s="1">
-        <v>0.118209453954305</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2057197677155297E-2</v>
+      </c>
+      <c r="N11" s="1"/>
+    </row>
+    <row r="12" spans="1:14" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1">
         <v>7.0585349758452001</v>
       </c>
       <c r="C12" s="1">
-        <v>0.116577694816434</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0785728319137698E-2</v>
+      </c>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1">
         <v>7.0753396553470003</v>
       </c>
       <c r="C13" s="1">
-        <v>0.117670638852321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1583374078481494E-2</v>
+      </c>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1">
         <v>7.0929763944296802</v>
       </c>
       <c r="C14" s="1">
-        <v>0.118098845799444</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1977352407887902E-2</v>
+      </c>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" spans="1:14" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1">
         <v>7.1058506533772503</v>
       </c>
       <c r="C15" s="1">
-        <v>0.11655919684067299</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0809253307868806E-2</v>
+      </c>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" spans="1:14" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1">
         <v>7.1002899790140797</v>
       </c>
       <c r="C16" s="1">
-        <v>0.118487075826876</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2274633741869796E-2</v>
+      </c>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1">
         <v>7.0521776395148397</v>
       </c>
       <c r="C17" s="1">
-        <v>0.117049111989703</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1163861413001701E-2</v>
+      </c>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1">
         <v>7.1167399746803</v>
       </c>
       <c r="C18" s="1">
-        <v>0.116964493443121</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1080103179609503E-2</v>
+      </c>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
@@ -2691,162 +2575,177 @@
         <v>7.1150966196750796</v>
       </c>
       <c r="C19" s="1">
-        <v>0.1174932059815</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1489922352594399E-2</v>
+      </c>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="1">
         <v>7.1580456374110897</v>
       </c>
       <c r="C20" s="1">
-        <v>0.118724780988732</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.24749435955321E-2</v>
+      </c>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" spans="1:14" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1">
         <v>7.2190634878376496</v>
       </c>
       <c r="C21" s="1">
-        <v>0.11857414162119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2335401313700993E-2</v>
+      </c>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" spans="1:14" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" s="1">
         <v>7.2062880356903998</v>
       </c>
       <c r="C22" s="1">
-        <v>0.116857985488521</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1016046887435004E-2</v>
+      </c>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="1:14" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B23" s="1">
         <v>7.1744031277414697</v>
       </c>
       <c r="C23" s="1">
-        <v>0.117839930521939</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1793854609833803E-2</v>
+      </c>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" spans="1:14" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1">
         <v>7.1782561712895996</v>
       </c>
       <c r="C24" s="1">
-        <v>0.116123290748398</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0459757856193396E-2</v>
+      </c>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="1:14" ht="42.75">
       <c r="A25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1">
         <v>7.1789296294298</v>
       </c>
       <c r="C25" s="1">
-        <v>0.116339626646247</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0535769763873494E-2</v>
+      </c>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" spans="1:14" ht="42.75">
       <c r="A26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B26" s="1">
         <v>7.1380410516405304</v>
       </c>
       <c r="C26" s="1">
-        <v>0.118521454357363</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2308774170074298E-2</v>
+      </c>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" ht="42.75">
       <c r="A27" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1">
         <v>7.1009576964689503</v>
       </c>
       <c r="C27" s="1">
-        <v>0.117743388207075</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.169315182519E-2</v>
+      </c>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" ht="42.75">
       <c r="A28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1">
         <v>7.1095475512566804</v>
       </c>
       <c r="C28" s="1">
-        <v>0.116823099810358</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.0973320989362394E-2</v>
+      </c>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" ht="42.75">
       <c r="A29" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1">
         <v>7.1520505928297498</v>
       </c>
       <c r="C29" s="1">
-        <v>0.118509294607666</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2289486690982594E-2</v>
+      </c>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" ht="42.75">
       <c r="A30" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="1">
         <v>7.1324554911158904</v>
       </c>
       <c r="C30" s="1">
-        <v>0.118631007440724</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2332804146897596E-2</v>
+      </c>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" ht="42.75">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31" s="1">
         <v>7.1772995060305798</v>
       </c>
       <c r="C31" s="1">
-        <v>0.117484320873481</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.1338576946075195E-2</v>
+      </c>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" ht="42.75">
       <c r="A32" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <v>7.13962874760949</v>
       </c>
       <c r="C32" s="1">
-        <v>0.118251546607688</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.2043650053371201E-2</v>
+      </c>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" ht="42.75">
       <c r="A33" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" s="1">
         <v>7.1606128880127899</v>
       </c>
       <c r="C33" s="1">
-        <v>0.118181098472526</v>
-      </c>
+        <v>9.2039900597932794E-2</v>
+      </c>
+      <c r="N33" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
